--- a/models/sovereigns/Tunisia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Tunisia_Sovereign_Model.xlsx
@@ -716,16 +716,34 @@
           <t>real_gdp_growth_pct</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
+      <c r="B6" s="2" t="n">
+        <v>2.1</v>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -884,16 +902,34 @@
           <t>current_account_pct_gdp</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
+      <c r="B14" s="2" t="n">
+        <v>-4.2</v>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -901,16 +937,34 @@
           <t>fdi_net_pct_gdp</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
+      <c r="B15" s="2" t="n">
+        <v>1.984</v>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>World Bank WDI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -918,16 +972,34 @@
           <t>gross_reserves_usd_bn</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n"/>
+      <c r="B16" s="2" t="n">
+        <v>9.343999999999999</v>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>World Bank WDI</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1052,16 +1124,34 @@
           <t>nominal_gdp_usd_bn</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n"/>
+      <c r="B22" s="2" t="n">
+        <v>60.745</v>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/models/sovereigns/Tunisia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Tunisia_Sovereign_Model.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Banque Centrale de Tunisie</t>
+          <t>Banque Centrale de Tunisie, Executive Board decision</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>INS</t>
+          <t>INS, Consumer Price Index release</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ministry of Finance</t>
+          <t>Ministry of Finance Tunisia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>total public debt (~82% of GDP)</t>
+          <t>Public debt, approximate</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>2026F</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ministry of Finance</t>
+          <t>Ministry of Finance Tunisia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>9.343999999999999</v>
+        <v>9.079000000000001</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -982,12 +982,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>World Bank WDI</t>
+          <t>IMF International Liquidity</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+          <t>Gross official reserves incl. gold at national valuation, end-month (auto-filled; a run's sourced point replaces it unless older)</t>
         </is>
       </c>
     </row>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Oct-26</t>
+          <t>06-Oct-26</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Banque Centrale de Tunisie</t>
+          <t>Banque Centrale de Tunisie, Daily Financial Indicators</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>net foreign exchange reserves (TND 23.7bn)</t>
+          <t>BCT net foreign exchange reserves, TND 23.7bn converted at approx. USD rate stated in source</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Oct-26</t>
+          <t>06-Oct-26</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Banque Centrale de Tunisie</t>
+          <t>Banque Centrale de Tunisie (92 days of imports, converted to months at 30.4 days)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Oct-26</t>
+          <t>Jul-26</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ministry of Finance</t>
+          <t>Ministry of Finance Tunisia (only remaining benchmark international bond: $150m 8.25% due 19-Sep-27, US066716AB78)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Frozen USD 1.9bn EFF agreed at staff level in Oct-22; no active Executive Board approval</t>
+          <t>USD 1.9bn Extended Fund Facility, staff-level agreement Oct-22, never approved by the Executive Board; frozen</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1334,7 +1334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1353,6 +1353,11 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>2026F</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Source</t>
         </is>
       </c>
@@ -1364,7 +1369,8 @@
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1373,7 +1379,8 @@
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1384,7 +1391,8 @@
       <c r="B4" s="2" t="n">
         <v>5.6</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" t="inlineStr">
         <is>
           <t>INS, 05-Oct-26</t>
         </is>
@@ -1397,7 +1405,8 @@
         </is>
       </c>
       <c r="B5" s="2" t="n"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1408,9 +1417,12 @@
       <c r="B6" s="2" t="n">
         <v>-5.2</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ministry of Finance, 08-Sep-26</t>
+      <c r="C6" s="2" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ministry of Finance Tunisia, 08-Sep-26</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1433,8 @@
         </is>
       </c>
       <c r="B7" s="2" t="n"/>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1432,9 +1445,10 @@
       <c r="B8" s="2" t="n">
         <v>82</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ministry of Finance, 08-Sep-26</t>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Ministry of Finance Tunisia, 08-Sep-26</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1459,8 @@
         </is>
       </c>
       <c r="B9" s="2" t="n"/>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1454,7 +1469,8 @@
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1463,7 +1479,8 @@
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1472,7 +1489,8 @@
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/models/sovereigns/Tunisia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Tunisia_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 08-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/tunisia.json</t>
+          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/tunisia.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Tunisia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Tunisia_Sovereign_Model.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>as of 08-Oct-26</t>
+          <t>as of 09-Oct-26</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Banque Centrale de Tunisie, Executive Board decision</t>
+          <t>Banque Centrale de Tunisie, Monetary Policy Statement</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ministry of Finance Tunisia</t>
+          <t>Ministry of Finance Tunisia, Budget Implementation Report</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Public debt, approximate</t>
+          <t>Public debt, approximate, as reported by Ministry of Finance</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026F</t>
+          <t>2026E</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ministry of Finance Tunisia</t>
+          <t>Ministry of Finance Tunisia, Budget Implementation Report</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>BCT net foreign exchange reserves, TND 23.7bn converted at approx. USD rate stated in source</t>
+          <t>BCT net foreign exchange reserves, TND 23.7bn (approx. USD 7.6bn as reported)</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Banque Centrale de Tunisie (92 days of imports, converted to months at 30.4 days)</t>
+          <t>Banque Centrale de Tunisie (92 days of imports, converted at 30.4 days per month)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>USD 1.9bn Extended Fund Facility, staff-level agreement Oct-22, never approved by the Executive Board; frozen</t>
+          <t>None active; USD 1.9bn EFF agreed at staff level Oct-22, never submitted to or approved by the Executive Board</t>
         </is>
       </c>
       <c r="C33" t="n">

--- a/models/sovereigns/Tunisia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Tunisia_Sovereign_Model.xlsx
@@ -700,7 +700,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>INS, Consumer Price Index release</t>
+          <t>Institut National de la Statistique (INS), CPI release</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Public debt, approximate, as reported by Ministry of Finance</t>
+          <t>Public debt, approximate</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>BCT net foreign exchange reserves, TND 23.7bn (approx. USD 7.6bn as reported)</t>
+          <t>BCT net foreign exchange reserves, TND 23.7bn converted at approx. USD (as stated in source)</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Banque Centrale de Tunisie (92 days of imports, converted at 30.4 days per month)</t>
+          <t>Banque Centrale de Tunisie (92 days of imports; ~3.0 months)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Jul-26</t>
+          <t>Oct-26</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ministry of Finance Tunisia (only remaining benchmark international bond: $150m 8.25% due 19-Sep-27, US066716AB78)</t>
+          <t>Ministry of Finance Tunisia, Debt Service Report (only remaining benchmark: $150m 8.25% due 19-Sep-27)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>None active; USD 1.9bn EFF agreed at staff level Oct-22, never submitted to or approved by the Executive Board</t>
+          <t>EFF (staff-level agreement Oct-22, never approved by Executive Board; frozen)</t>
         </is>
       </c>
       <c r="C33" t="n">

--- a/models/sovereigns/Tunisia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Tunisia_Sovereign_Model.xlsx
@@ -647,12 +647,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Oct-26</t>
+          <t>07-Oct-26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Banque Centrale de Tunisie, Monetary Policy Statement</t>
+          <t>Banque Centrale de Tunisie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Institut National de la Statistique (INS), CPI release</t>
+          <t>Institut National de la Statistique</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ministry of Finance Tunisia, Budget Implementation Report</t>
+          <t>Ministry of Finance Tunisia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ministry of Finance Tunisia, Budget Implementation Report</t>
+          <t>Ministry of Finance Tunisia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Banque Centrale de Tunisie, Daily Financial Indicators</t>
+          <t>Banque Centrale de Tunisie</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>BCT net foreign exchange reserves, TND 23.7bn converted at approx. USD (as stated in source)</t>
+          <t>BCT net foreign exchange reserves, TND 23.7bn converted at ~USD as stated in source (approx.)</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Banque Centrale de Tunisie (92 days of imports; ~3.0 months)</t>
+          <t>Banque Centrale de Tunisie (92 days of imports, converted to months)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EFF (staff-level agreement Oct-22, never approved by Executive Board; frozen)</t>
+          <t>$1.9bn Extended Fund Facility agreed at staff level Oct-22; never approved by the Executive Board; frozen</t>
         </is>
       </c>
       <c r="C33" t="n">

--- a/models/sovereigns/Tunisia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Tunisia_Sovereign_Model.xlsx
@@ -647,12 +647,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>07-Oct-26</t>
+          <t>Oct-26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Banque Centrale de Tunisie</t>
+          <t>Banque Centrale de Tunisie, Executive Board decision</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Institut National de la Statistique</t>
+          <t>Institut National de la Statistique (INS), CPI release</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Public debt, approximate</t>
+          <t>Public debt, approximate estimate</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ministry of Finance Tunisia</t>
+          <t>Ministry of Finance Tunisia (deficit projection ~5.2% of GDP)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Banque Centrale de Tunisie</t>
+          <t>Banque Centrale de Tunisie, daily financial indicators</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>BCT net foreign exchange reserves, TND 23.7bn converted at ~USD as stated in source (approx.)</t>
+          <t>BCT net foreign exchange reserves, TND 23.7bn converted at approx. USD rate as stated in source (approximately $7.6bn)</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Banque Centrale de Tunisie (92 days of imports, converted to months)</t>
+          <t>Banque Centrale de Tunisie, daily financial indicators (92 days of imports, converted to months at 30.4 days)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>$1.9bn Extended Fund Facility agreed at staff level Oct-22; never approved by the Executive Board; frozen</t>
+          <t>$1.9bn Extended Fund Facility agreed at staff level Oct-22; never approved by the Executive Board (frozen)</t>
         </is>
       </c>
       <c r="C33" t="n">

--- a/models/sovereigns/Tunisia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Tunisia_Sovereign_Model.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Banque Centrale de Tunisie, Executive Board decision</t>
+          <t>Banque Centrale de Tunisie, Executive Board meeting</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Institut National de la Statistique (INS), CPI release</t>
+          <t>INS Consumer Price Index release</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ministry of Finance Tunisia</t>
+          <t>Ministry of Finance Tunisia, budget implementation report</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ministry of Finance Tunisia (deficit projection ~5.2% of GDP)</t>
+          <t>Ministry of Finance Tunisia, budget implementation report (deficit projected at approx. 5.2% of GDP)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>BCT net foreign exchange reserves, TND 23.7bn converted at approx. USD rate as stated in source (approximately $7.6bn)</t>
+          <t>BCT net foreign exchange reserves, TND 23.7bn converted at approx. USD 7.6bn as stated in source</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Banque Centrale de Tunisie, daily financial indicators (92 days of imports, converted to months at 30.4 days)</t>
+          <t>Banque Centrale de Tunisie (92 days of imports, converted to months at 30.4 days)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>$1.9bn Extended Fund Facility agreed at staff level Oct-22; never approved by the Executive Board (frozen)</t>
+          <t>USD 1.9bn Extended Fund Facility agreed at staff level Oct-22; never approved by the Executive Board; frozen</t>
         </is>
       </c>
       <c r="C33" t="n">

--- a/models/sovereigns/Tunisia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Tunisia_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/tunisia.json</t>
+          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/tunisia.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Tunisia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Tunisia_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/tunisia.json</t>
+          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/tunisia.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Tunisia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Tunisia_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/tunisia.json</t>
+          <t>built 26-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/tunisia.json</t>
         </is>
       </c>
     </row>
